--- a/zy70510/test_export_result.xlsx
+++ b/zy70510/test_export_result.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,12 +529,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RCP20260516034427B548206C</t>
+          <t>RCP20260516052629BD5E875D</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BAT20260516034427AFC3F8</t>
+          <t>BAT20260516052629C440A5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>test_batch_1778903067</t>
+          <t>test_batch_1778909188</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -594,18 +594,241 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-05-16 03:44:27</t>
+          <t>2026-05-16 05:26:29</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-05-16 03:44:27</t>
+          <t>2026-05-16 05:26:29</t>
         </is>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>RCP20260516052609E540C055</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BAT2026051605260926A3BA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>状态机测试</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>test_state_1778909169</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>manual_fixed</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>人工修正测试</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>{"total": 1, "success": 0, "failed": 0}</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>{"test": "state_test"}</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2026-05-16 05:26:09</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2026-05-16 05:26:09</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RCP20260516052609C7B15E6A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BAT20260516052609B2B561</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>重复计数测试</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>test_count_1778909169</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>{"test": "count_test"}</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2026-05-16 05:26:09</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>RCP202605160526085FC6F399</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BAT2026051605260836FBE2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>用户批量导入测试</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>test_batch_1778909168</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>manual_fixed</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>经人工核查，user_003数据虽格式有误，但为历史遗留问题，予以特殊通过。整体批次标记为完成。</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>{"total": 3, "success": 3, "failed": 0, "manual_fixed": true}</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>{"file_name": "users_20240115.xlsx", "upload_time": "2024-01-15 10:30:00", "operator": "admin"}</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>{"total": 3, "success": 2, "failed": 1, "duration_seconds": 5.2}</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2026-05-16 05:26:08</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2026-05-16 05:26:08</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>2026-05-16 05:26:08</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -618,7 +841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -676,12 +899,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RCP20260516034427B548206C</t>
+          <t>RCP20260516052629BD5E875D</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DTL2026051603442727A4DF</t>
+          <t>DTL20260516052629C5719E</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -712,7 +935,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-05-16 03:44:27</t>
+          <t>2026-05-16 05:26:29</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -722,12 +945,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RCP20260516034427B548206C</t>
+          <t>RCP20260516052629BD5E875D</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DTL20260516034427BF726C</t>
+          <t>DTL2026051605262900A174</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -758,7 +981,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-05-16 03:44:27</t>
+          <t>2026-05-16 05:26:29</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -768,12 +991,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RCP20260516034427B548206C</t>
+          <t>RCP20260516052629BD5E875D</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DTL20260516034427B2C6A5</t>
+          <t>DTL20260516052629FC1556</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -808,10 +1031,228 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-05-16 03:44:27</t>
+          <t>2026-05-16 05:26:29</t>
         </is>
       </c>
       <c r="J4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>RCP20260516052609E540C055</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DTL202605160526092218E3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>item_001</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>{"item_key": "item_001", "name": "测试项1"}</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RCP20260516052609C7B15E6A</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DTL20260516052609E841EE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>item_001</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>{"item_key": "item_001", "name": "测试项1"}</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>{"id": 1}</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-05-16 05:26:09</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RCP202605160526085FC6F399</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DTL20260516052608372EA6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>user_001</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>{"item_key": "user_001", "name": "张三", "email": "zhangsan@test.com"}</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>{"user_id": 1001, "status": "created"}</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>{"rule": "auto_create", "version": "v1.0"}</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-05-16 05:26:08</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RCP202605160526085FC6F399</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DTL202605160526088668E3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>user_002</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>{"item_key": "user_002", "name": "李四", "email": "lisi@test.com"}</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>{"user_id": 1002, "status": "created"}</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>{"rule": "auto_create", "version": "v1.0"}</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-05-16 05:26:08</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RCP202605160526085FC6F399</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DTL202605160526082CC704</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>user_003</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>{"item_key": "user_003", "name": "王五", "email": "wangwu@test.com"}</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>{"user_id": 1003, "status": "manual_approved"}</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>邮箱格式不符合要求</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>{"rule": "manual_exception", "approved_by": "manager"}</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-05-16 05:26:08</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
         <v>1</v>
       </c>
     </row>

--- a/zy70510/test_export_result.xlsx
+++ b/zy70510/test_export_result.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,12 +529,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RCP20260516052629BD5E875D</t>
+          <t>RCP202605160700168B0C3FA6</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BAT20260516052629C440A5</t>
+          <t>BAT20260516070016CE8A9C</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>test_batch_1778909188</t>
+          <t>test_batch_1778914816</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-05-16 05:26:29</t>
+          <t>2026-05-16 07:00:16</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-05-16 05:26:29</t>
+          <t>2026-05-16 07:00:16</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -610,22 +610,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RCP20260516052609E540C055</t>
+          <t>RCP202605160700081C10E67B</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BAT2026051605260926A3BA</t>
+          <t>BAT20260516070008FFC3C9</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>状态机测试</t>
+          <t>终态切换测试</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>test_state_1778909169</t>
+          <t>test_state_switch_1778914808</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -635,50 +635,34 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>manual_fixed</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>人工修正测试</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>{"total": 1, "success": 0, "failed": 0}</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>{"test": "state_test"}</t>
+          <t>{"test": "state_switch"}</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>system</t>
-        </is>
-      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-05-16 05:26:09</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>2026-05-16 05:26:09</t>
-        </is>
-      </c>
+          <t>2026-05-16 07:00:08</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -687,22 +671,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RCP20260516052609C7B15E6A</t>
+          <t>RCP20260516070008CA8BA4B0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BAT20260516052609B2B561</t>
+          <t>BAT20260516070008DA81D2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>重复计数测试</t>
+          <t>状态机测试</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>test_count_1778909169</t>
+          <t>test_state_1778914808</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -712,34 +696,50 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>manual_fixed</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>人工修正测试</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>{"total": 1, "success": 0, "failed": 0}</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>{"test": "count_test"}</t>
+          <t>{"test": "state_test"}</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-05-16 05:26:09</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+          <t>2026-05-16 07:00:08</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2026-05-16 07:00:08</t>
+        </is>
+      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -748,85 +748,146 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RCP202605160526085FC6F399</t>
+          <t>RCP2026051607000890C4DDD7</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BAT2026051605260836FBE2</t>
+          <t>BAT20260516070008BE0D1E</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>重复计数测试</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>test_count_1778914808</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>{"test": "count_test"}</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2026-05-16 07:00:08</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RCP20260516070008ACD6368F</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BAT20260516070008C22B16</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>用户批量导入测试</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>test_batch_1778909168</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>test_batch_1778914808</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>manual_fixed</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="G6" t="n">
         <v>3</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H6" t="n">
         <v>2</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I6" t="n">
         <v>1</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>经人工核查，user_003数据虽格式有误，但为历史遗留问题，予以特殊通过。整体批次标记为完成。</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>{"total": 3, "success": 3, "failed": 0, "manual_fixed": true}</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>{"file_name": "users_20240115.xlsx", "upload_time": "2024-01-15 10:30:00", "operator": "admin"}</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>{"total": 3, "success": 2, "failed": 1, "duration_seconds": 5.2}</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
         <is>
           <t>system</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2026-05-16 05:26:08</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>2026-05-16 05:26:08</t>
-        </is>
-      </c>
-      <c r="R5" t="n">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2026-05-16 07:00:08</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2026-05-16 07:00:08</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
         <v>1</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>2026-05-16 05:26:08</t>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>2026-05-16 07:00:08</t>
         </is>
       </c>
     </row>
@@ -841,7 +902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -899,12 +960,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RCP20260516052629BD5E875D</t>
+          <t>RCP202605160700168B0C3FA6</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DTL20260516052629C5719E</t>
+          <t>DTL20260516070016D1044A</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -935,7 +996,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-05-16 05:26:29</t>
+          <t>2026-05-16 07:00:16</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -945,12 +1006,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RCP20260516052629BD5E875D</t>
+          <t>RCP202605160700168B0C3FA6</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DTL2026051605262900A174</t>
+          <t>DTL20260516070016399B91</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -981,7 +1042,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-05-16 05:26:29</t>
+          <t>2026-05-16 07:00:16</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -991,12 +1052,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RCP20260516052629BD5E875D</t>
+          <t>RCP202605160700168B0C3FA6</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DTL20260516052629FC1556</t>
+          <t>DTL20260516070016AAF61D</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1031,7 +1092,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-05-16 05:26:29</t>
+          <t>2026-05-16 07:00:16</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -1041,12 +1102,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RCP20260516052609E540C055</t>
+          <t>RCP202605160700081C10E67B</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DTL202605160526092218E3</t>
+          <t>DTL202605160700082A521A</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1056,7 +1117,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>success</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1064,23 +1125,31 @@
           <t>{"item_key": "item_001", "name": "测试项1"}</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>{"id": 1, "fixed": true}</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-05-16 07:00:08</t>
+        </is>
+      </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RCP20260516052609C7B15E6A</t>
+          <t>RCP20260516070008CA8BA4B0</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DTL20260516052609E841EE</t>
+          <t>DTL20260516070008E4A59B</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1090,7 +1159,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1098,36 +1167,28 @@
           <t>{"item_key": "item_001", "name": "测试项1"}</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>{"id": 1}</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-05-16 05:26:09</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RCP202605160526085FC6F399</t>
+          <t>RCP2026051607000890C4DDD7</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DTL20260516052608372EA6</t>
+          <t>DTL20260516070008778573</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>user_001</t>
+          <t>item_001</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1137,43 +1198,39 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>{"item_key": "user_001", "name": "张三", "email": "zhangsan@test.com"}</t>
+          <t>{"item_key": "item_001", "name": "测试项1"}</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>{"user_id": 1001, "status": "created"}</t>
+          <t>{"id": 1}</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>{"rule": "auto_create", "version": "v1.0"}</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-05-16 05:26:08</t>
+          <t>2026-05-16 07:00:08</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RCP202605160526085FC6F399</t>
+          <t>RCP20260516070008ACD6368F</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DTL202605160526088668E3</t>
+          <t>DTL20260516070008ADC719</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>user_002</t>
+          <t>user_001</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1183,12 +1240,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>{"item_key": "user_002", "name": "李四", "email": "lisi@test.com"}</t>
+          <t>{"item_key": "user_001", "name": "张三", "email": "zhangsan@test.com"}</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>{"user_id": 1002, "status": "created"}</t>
+          <t>{"user_id": 1001, "status": "created"}</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1199,7 +1256,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-05-16 05:26:08</t>
+          <t>2026-05-16 07:00:08</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -1209,50 +1266,96 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RCP202605160526085FC6F399</t>
+          <t>RCP20260516070008ACD6368F</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DTL202605160526082CC704</t>
+          <t>DTL2026051607000860F9A2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>user_002</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>{"item_key": "user_002", "name": "李四", "email": "lisi@test.com"}</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>{"user_id": 1002, "status": "created"}</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>{"rule": "auto_create", "version": "v1.0"}</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-05-16 07:00:08</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>RCP20260516070008ACD6368F</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DTL20260516070008718535</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>user_003</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>{"item_key": "user_003", "name": "王五", "email": "wangwu@test.com"}</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>{"user_id": 1003, "status": "manual_approved"}</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>邮箱格式不符合要求</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>{"rule": "manual_exception", "approved_by": "manager"}</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-05-16 05:26:08</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-05-16 07:00:08</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
         <v>1</v>
       </c>
     </row>
